--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-steps","columns-stats","cards-product","tabs-showcase","tabs-testimonial","cards","hero-cta"]</t>
+    <t>["hero","columns-stats","cards-product","tabs-showcase","tabs-testimonial","cards","hero-cta"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-06T15:32:16.448Z</t>
+    <t>2026-05-06T18:39:21.862Z</t>
   </si>
   <si>
     <t>Font Management, Licensing &amp; Typography Platform | Monotype</t>
